--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store_Product_Catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tour_Packages_Catalog" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D5C75"/>
-        <bgColor rgb="000D5C75"/>
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F8FA"/>
-        <bgColor rgb="00F0F8FA"/>
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,32 +66,38 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,534 +464,578 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Product SKU</t>
+          <t>Package Code</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product Name</t>
+          <t>Package Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Destination</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Regular Price ($)</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sale Price ($)</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Stock Status &amp; Inventory</t>
+          <t>Standard Price ($)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Key Specifications &amp; Features</t>
+          <t>Discounted Price ($)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Warranty &amp; Return Policy</t>
+          <t>Availability &amp; Group Size</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Included Services</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Excluded Services</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Key Highlights &amp; Itinerary</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Customer Rating &amp; Reviews</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LUM-AUD-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>LuminaSound Elite Wireless Headphones</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Audio &amp; Sound</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>$249.99</t>
+          <t>ROAM-PK-01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Hunza Adventure &amp; Cultural Odyssey</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Hunza Valley &amp; Karimabad</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$199.99</t>
+          <t>5 Days / 4 Nights</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>In Stock (85 units available)</t>
+          <t>$599</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Hybrid Active Noise Cancellation (up to 38dB), 40-hour battery life, USB-C fast charge (10 mins = 4 hours), multipoint Bluetooth 5.3, custom 40mm beryllium drivers, fold-flat design with carrying case</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1-Year Manufacturer Warranty included. 30-Day Hassle-Free Returns. Eligible for LuminaCare 2-Year Drop &amp; Spill Protection ($29.99).</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>4.8 / 5.0 (1,420 customer reviews)</t>
+          <t>$499</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Available Weekly (Min 2, Max 12 persons)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>4-star hotel stay with mountain views, chauffeured 4x4 Prado, professional local guide, breakfast &amp; dinners, Attabad Lake boating passes, Altit &amp; Baltit Fort entry fees.</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>International flights, personal shopping, lunch meals, travel insurance.</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Scenic Karakoram Highway drive, sunrise over Rakaposhi (7,788m), exploration of ancient 800-year-old Baltit Fort, turquoise waters of Attabad Lake, Passu Cones suspension bridge walk.</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>4.9 / 5.0 (340 reviews) - 'Life-changing mountain views and warm hospitality.'</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>LUM-WCH-02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>LuminaPulse Ultra Smartwatch</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Wearables &amp; Fitness</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>$179.99</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>$149.99</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>In Stock (140 units available)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>1.43-inch AMOLED Always-On Display, optical heart rate, ECG rhythm tracking, Blood Oxygen (SpO2), 110+ sports modes, 5ATM water resistant (swim-proof up to 50m), 7-day battery life, compatible with iOS &amp; Android</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>1-Year Manufacturer Warranty. 30-Day Money-Back Guarantee. LuminaCare 3-Year Battery &amp; Accidental Plan ($49.99).</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>4.7 / 5.0 (980 customer reviews)</t>
+    <row r="3" ht="55" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ROAM-UAE-02</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Luxury Escape &amp; Desert Safari</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Dubai City &amp; Arabian Desert</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>4 Days / 3 Nights</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>$849</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>$699</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Available Daily (Private or Small Group)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>5-star hotel in Downtown Dubai or Marina, private airport transfers, 4x4 desert dune bashing safari with BBQ dinner &amp; show, Burj Khalifa 124th floor ticket, Dubai Marina yacht dinner cruise.</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>UAE tourist visa fee, personal shopping, alcoholic beverages during desert safari.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Spectacular views from Burj Khalifa, thrilling 4x4 desert safari with sandboarding and camel rides, luxury Marina yacht cruise at sunset, exploration of Old Dubai Gold &amp; Spice Souks.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>4.8 / 5.0 (520 reviews) - 'Flawless luxury arrangements and hassle-free VIP transfers.'</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
+    <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LUM-SMH-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>LuminaGlow Smart Ambient LED Light Strip</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Smart Home Lighting</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>$49.99</t>
+          <t>ROAM-ID-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Bali Tropical Retreat &amp; Island Wellness</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ubud &amp; Seminyak</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>$39.99</t>
+          <t>6 Days / 5 Nights</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>In Stock (310 units available)</t>
+          <t>$950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16.4 ft (5 meters) length, 16 million RGB colors + tunable warm-to-cool whites, Wi-Fi 2.4GHz &amp; Bluetooth app control, works seamlessly with Amazon Alexa, Apple HomeKit &amp; Google Assistant, built-in mic for music rhythmic synchronization</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1-Year Replacement Warranty. 30-Day Return window (must be unused in original packaging).</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4.6 / 5.0 (2,150 customer reviews)</t>
+          <t>$799</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Available Year-Round (Solo, Couples, Families)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Private villa with plunge pool in Ubud, beach resort in Seminyak, daily breakfast, private air-conditioned van &amp; driver, sacred Tirta Empul temple tour, Uluwatu sunset fire dance tickets.</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>International airfare, lunch/dinners not specified, personal spa treatments.</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Iconic Tegallalang rice terrace jungle swing, tranquil wellness spa sessions, sunset at Uluwatu Cliff Temple with Kecak dance, day excursion to Nusa Penida crystalline beaches.</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>4.9 / 5.0 (410 reviews) - 'The perfect blend of relaxation, vibrant culture, and tropical nature.'</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>LUM-ACC-04</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>LuminaVault 65W GaN Fast Charger</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Charging &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>$39.99</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>$29.99</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>In Stock (420 units available)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Next-gen Gallium Nitride (GaN) technology, 3 ports (2x USB-C Power Delivery 3.0 + 1x USB-A QuickCharge 4.0), foldable prongs, compact travel size (50% smaller than standard chargers), powers MacBook, iPhone, Galaxy, iPad simultaneously</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2-Year Extended Hardware Warranty included free. 30-Day Return Window.</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>4.9 / 5.0 (3,410 customer reviews)</t>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ROAM-PK-04</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Skardu Karakoram &amp; Turquoise Lakes Expedition</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Skardu &amp; Shigar Valley</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>6 Days / 5 Nights</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>$749</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>$649</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>May through October (Small Group 4-10 persons)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Stay at Shangrila Resort &amp; Shigar Serena Fort, 4x4 mountain jeeps, daily breakfast &amp; dinner, dedicated mountain guide, permits for Deosai Plains.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Flights to/from Islamabad, high-altitude gear rental, tipping.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Shangrila Lake (Lower Kachura), boat tour on Upper Kachura Lake, sunset over the Cold Desert of Katpana, Deosai National Park ('Land of Giants'), historic Shigar Fort heritage walk.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>4.9 / 5.0 (280 reviews) - 'Unreal landscapes, like stepping into another planet.'</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
+    <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LUM-CAM-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>LuminaVision 2K Outdoor Security Camera</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Smart Home Security</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>$89.99</t>
+          <t>ROAM-TR-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Istanbul Two Continents Heritage &amp; Culinary Journey</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Istanbul (European &amp; Asian sides)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>$69.99</t>
+          <t>5 Days / 4 Nights</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>In Stock (115 units available)</t>
+          <t>$720</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2K QHD resolution (2560x1440), full color night vision with dual motion spotlights, 2-way audio intercom, AI person &amp; vehicle detection, IP65 waterproof weatherproof rating, solar-panel compatible, microSD local storage (up to 256GB) or cloud</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1-Year Manufacturer Warranty. 30-Day Free Returns. Free replacement if damaged by weather within warranty.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4.6 / 5.0 (740 customer reviews)</t>
+          <t>$599</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Available Weekly (Year-Round)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Boutique hotel in Sultanahmet, private Bosphorus yacht sunset cruise, skip-the-line passes to Hagia Sophia, Topkapi Palace &amp; Basilica Cistern, guided Grand Bazaar culinary walking tour.</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Turkish e-Visa, international airfare, optional Turkish bath (Hammam) session.</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Walking through 1,500 years of history at Hagia Sophia, tasting authentic kebabs and baklava in Kadıköy, sunset cruise across the continental divide between Europe and Asia.</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>4.7 / 5.0 (310 reviews) - 'Knowledgeable guides and unforgettable food tastings.'</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>LUM-KEY-06</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>LuminaTactile Pro Wireless Mechanical Keyboard</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Computer Accessories</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>$129.99</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>$109.99</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>In Stock (65 units available)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>75% compact layout (84 keys), hot-swappable linear red switches, PBT double-shot keycaps, south-facing per-key RGB backlighting, tri-mode connectivity (Bluetooth 5.1, 2.4GHz wireless dongle, USB-C wired), Mac &amp; Windows compatible</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>1-Year Limited Warranty. 30-Day Return Policy. Switch puller and spare keycaps included in box.</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>4.8 / 5.0 (610 customer reviews)</t>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ROAM-FR-06</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Paris Romance, Art &amp; Gastronomy</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Paris &amp; Versailles</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>5 Days / 4 Nights</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>$1,199</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>$999</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Available Year-Round (Couples &amp; Private Groups)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>4-star boutique hotel near Saint-Germain-des-Prés, Seine River champagne cruise, Eiffel Tower summit tickets, guided Louvre Museum tour, private day excursion to Palace of Versailles.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Schengen visa fees, international flights, discretionary guide tips.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Eiffel Tower panoramic summit visit, Mona Lisa VIP viewing, stroll through cobblestone streets of Montmartre, royal gardens and Hall of Mirrors at Versailles.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>4.8 / 5.0 (215 reviews) - 'Magical romantic getaway arranged to absolute perfection.'</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
+    <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LUM-HUB-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>LuminaDock 10-in-1 USB-C Hub &amp; Docking Station</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Computer Accessories</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>$79.99</t>
+          <t>ROAM-PK-07</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Northern Pakistan Grand Circuit (Hunza + Skardu)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Gilgit, Hunza &amp; Baltistan</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>$64.99</t>
+          <t>10 Days / 9 Nights</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>In Stock (200 units available)</t>
+          <t>$1,399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Dual 4K HDMI video output (dual monitor support 60Hz), 100W Power Delivery pass-through charging, Gigabit Ethernet (1000Mbps), SD/TF 4.0 card reader (up to 312MB/s), 3x USB 3.2 Gen 1 ports (5Gbps), precision aluminum unibody enclosure</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1-Year Hardware Warranty. 30-Day Return Policy. Protected against overheating and voltage spikes.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4.7 / 5.0 (1,120 customer reviews)</t>
+          <t>$1,199</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>June through September (Weekly Departures)</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>All boutique &amp; resort accommodations, private Toyota Land Cruiser with fuel &amp; mountain driver, all meals (breakfast, lunch, dinner), national park entry fees, cultural folk music night.</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Islamabad hotel prior to departure, domestic flight Islamabad-Gilgit (if requested), personal porter fees.</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>The ultimate northern expedition connecting Hunza's apricot orchards and Karakoram Highway with Skardu's turquoise lakes and Deosai high-altitude plateau.</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>5.0 / 5.0 (190 reviews) - 'The undisputed ultimate road trip of a lifetime.'</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>LUM-ROB-08</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>LuminaClean X7 Robot Vacuum &amp; Sonic Mop</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Smart Appliances</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>$399.99</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>$329.99</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Low Stock (42 units available)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Precision LiDAR laser mapping, 4000Pa ultra-strong suction, sonic vibration wet mopping (3000 scrubs/min), automatic ultrasonic carpet detection &amp; mop auto-lift, 5200mAh battery (up to 180 min runtime), automatic self-recharging and resume</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>1-Year Comprehensive Warranty (motors, sensors &amp; battery). 30-Day Return Window. LuminaCare 3-Year Plan available ($49.99).</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>4.8 / 5.0 (890 customer reviews)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>LUM-SPK-09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>LuminaBoom 360 Portable Waterproof Speaker</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Audio &amp; Sound</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>$69.99</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>$54.99</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>In Stock (180 units available)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>360-degree omnidirectional sound, dual passive bass radiators, IPX7 100% waterproof (floats in pool/lake), 24-hour non-stop battery life, True Wireless Stereo (TWS) pairing allows syncing two units, shockproof rubberized bumper</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1-Year Limited Warranty. 30-Day Return Policy. Free return shipping for store credit.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4.9 / 5.0 (2,850 customer reviews)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>LUM-AIR-10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>LuminaPure H13 Smart HEPA Air Purifier</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Smart Appliances</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>$119.99</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>$99.99</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>In Stock (90 units available)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Medical-grade H13 True HEPA 4-stage filtration, removes 99.97% of airborne dust, pollen, pet dander, smoke and odor, covers up to 1,000 sq ft, whisper-quiet sleep mode (22dB), real-time laser PM2.5 air quality sensor with 4-color light ring</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>2-Year Warranty on motor &amp; electronics. 30-Day Money-Back Guarantee. Replacement filters available for $24.99.</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>4.7 / 5.0 (1,340 customer reviews)</t>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ROAM-PK-08</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Swat Valley &amp; Kalam Alpine Discovery</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Swat Valley, Kalam &amp; Malam Jabba</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>4 Days / 3 Nights</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>$450</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>$380</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Available Weekly (March through November)</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Riverside resort in Fizagat &amp; Kalam, private air-conditioned Prado with driver, daily breakfast &amp; dinner, local guide, Malam Jabba chairlift &amp; zipline passes, Mahodand Lake 4x4 jeep safari.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Lunch meals, personal shopping, optional skiing gear rental.</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Explore the Switzerland of the East: Malam Jabba ski slope views, scenic Ushu pine forest walk, turquoise Mahodand Lake excursion, Mingora traditional handicrafts bazaar.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>4.9 / 5.0 (260 reviews) - 'Breathtaking green valleys, river views, and fantastic mountain air.'</t>
         </is>
       </c>
     </row>
